--- a/data/trans_orig/IP3111_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3111_2023-Estudios-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>593</t>
+          <t>526</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6030</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1206</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>9409</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2261</t>
+          <t>2878</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,48%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>2953</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16279</t>
+          <t>14764</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3889</t>
+          <t>3772</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12888</t>
+          <t>12894</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8671</t>
+          <t>9106</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24381</t>
+          <t>24997</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9491</t>
+          <t>9280</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29941</t>
+          <t>29759</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>56,3%</t>
+          <t>55,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9527</t>
+          <t>9274</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>21611</t>
+          <t>20782</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>15,89%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>37,04%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>21610</t>
+          <t>22136</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>45909</t>
+          <t>46324</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,16%</t>
+          <t>41,54%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6112</t>
+          <t>6245</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21141</t>
+          <t>21604</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,75%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4191</t>
+          <t>3904</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15298</t>
+          <t>15124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13146</t>
+          <t>12492</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>32383</t>
+          <t>30568</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>27,41%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3037</t>
+          <t>2842</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11311</t>
+          <t>11831</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2840</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10888</t>
+          <t>10712</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,66%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7576</t>
+          <t>7205</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18382</t>
+          <t>18805</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>4596</t>
+          <t>4526</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15411</t>
+          <t>15216</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>28,61%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12378</t>
+          <t>12772</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25552</t>
+          <t>25954</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,48%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19331</t>
+          <t>19738</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37831</t>
+          <t>37014</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,19%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>43853</t>
+          <t>44480</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>70875</t>
+          <t>70550</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>38351</t>
+          <t>39331</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>61156</t>
+          <t>60507</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>88895</t>
+          <t>89835</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124154</t>
+          <t>124884</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>50721</t>
+          <t>51225</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81401</t>
+          <t>80844</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>78942</t>
+          <t>79468</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>116277</t>
+          <t>115423</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>139148</t>
+          <t>139608</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>188803</t>
+          <t>189078</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,89%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78303</t>
+          <t>76394</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>113306</t>
+          <t>112981</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96181</t>
+          <t>95945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132276</t>
+          <t>131848</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>184794</t>
+          <t>183415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>234123</t>
+          <t>233983</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,61%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>66372</t>
+          <t>65759</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100765</t>
+          <t>99498</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,43%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72217</t>
+          <t>70072</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102741</t>
+          <t>102703</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>13,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>143865</t>
+          <t>148028</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>190983</t>
+          <t>193919</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>59867</t>
+          <t>61009</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>160280</t>
+          <t>173694</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58363</t>
+          <t>58320</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>91696</t>
+          <t>93959</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>131165</t>
+          <t>130836</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>237962</t>
+          <t>242630</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,76%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>25,52%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>43637</t>
+          <t>43575</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>71035</t>
+          <t>72930</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2105,12 +2105,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>60971</t>
+          <t>61724</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>113684</t>
+          <t>114374</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>114684</t>
+          <t>113578</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>174590</t>
+          <t>175854</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>24840</t>
+          <t>24565</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>41911</t>
+          <t>42767</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>29,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2355,12 +2355,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>25414</t>
+          <t>24590</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>44813</t>
+          <t>45144</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2370,12 +2370,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>13,58%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54597</t>
+          <t>54724</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>80160</t>
+          <t>82157</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>27873</t>
+          <t>28088</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>45003</t>
+          <t>45259</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>46245</t>
+          <t>47153</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71734</t>
+          <t>71082</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,53%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80300</t>
+          <t>80433</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>108766</t>
+          <t>111565</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20032</t>
+          <t>18960</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>34610</t>
+          <t>34231</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29753</t>
+          <t>29162</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50331</t>
+          <t>49612</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53380</t>
+          <t>52970</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78346</t>
+          <t>78569</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,31%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,0%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>17001</t>
+          <t>16635</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31014</t>
+          <t>31513</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22664</t>
+          <t>22492</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42034</t>
+          <t>41475</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,42%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>43152</t>
+          <t>42773</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>66752</t>
+          <t>66652</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>9978</t>
+          <t>9906</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>22400</t>
+          <t>22437</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,35%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8217</t>
+          <t>8965</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21595</t>
+          <t>21507</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20815</t>
+          <t>20714</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38143</t>
+          <t>38391</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7541</t>
+          <t>7586</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19913</t>
+          <t>19618</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2900,12 +2900,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9962</t>
+          <t>9940</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11087</t>
+          <t>11634</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>25625</t>
+          <t>26298</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>76951</t>
+          <t>75935</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>108943</t>
+          <t>110232</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72019</t>
+          <t>71916</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>103203</t>
+          <t>105058</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3165,12 +3165,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>156197</t>
+          <t>156934</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>202459</t>
+          <t>203571</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>90595</t>
+          <t>90011</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>128349</t>
+          <t>129160</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>141526</t>
+          <t>140045</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>186054</t>
+          <t>186041</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>241540</t>
+          <t>240054</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>302040</t>
+          <t>301333</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>21,69%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>119943</t>
+          <t>116548</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>163075</t>
+          <t>162488</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,05%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>146851</t>
+          <t>146559</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>189445</t>
+          <t>188540</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>279436</t>
+          <t>272159</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>340815</t>
+          <t>336429</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>24,21%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>98335</t>
+          <t>99901</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>140345</t>
+          <t>140248</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>106512</t>
+          <t>107541</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>146789</t>
+          <t>145141</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>14,52%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>215347</t>
+          <t>218191</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>271252</t>
+          <t>272756</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,7%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>80397</t>
+          <t>79571</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>209519</t>
+          <t>193967</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>77547</t>
+          <t>76601</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>118360</t>
+          <t>116508</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>169045</t>
+          <t>171357</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>286167</t>
+          <t>279004</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -3680,12 +3680,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>64512</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>96677</t>
+          <t>96707</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>82406</t>
+          <t>83954</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>141050</t>
+          <t>144583</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>157768</t>
+          <t>156323</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>226514</t>
+          <t>222235</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>16,3%</t>
+          <t>15,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP3111_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP3111_2023-Estudios-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2803</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6670</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>5,22%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>12,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2201</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>526</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6030</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,14%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3901</t>
+          <t>2039</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1206</t>
+          <t>528</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8497</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>6102</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2878</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11693</t>
+          <t>9355</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>9,43%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6338</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>3467</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>11001</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>6,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>7337</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2953</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14764</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13,8%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>27,76%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7393</t>
+          <t>5738</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3772</t>
+          <t>2723</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12894</t>
+          <t>10242</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>14730</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>9106</t>
+          <t>7020</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>24997</t>
+          <t>18460</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>12,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,41%</t>
+          <t>18,6%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>13476</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>8570</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>20338</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>25,09%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>15,96%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>37,86%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>16509</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>9280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>29759</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>31,04%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>17,45%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>55,95%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14652</t>
+          <t>12303</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>7985</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>20782</t>
+          <t>18394</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15,89%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>31161</t>
+          <t>25779</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>22136</t>
+          <t>18840</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>46324</t>
+          <t>33788</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>27,94%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>7276</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3442</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13376</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>13,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>24,9%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>11827</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>6245</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>21604</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>22,24%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>11,74%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>40,62%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3904</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>15124</t>
+          <t>14073</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>19,91%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>19956</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12492</t>
+          <t>10609</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>30568</t>
+          <t>23656</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>23,84%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6329</t>
+          <t>5673</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2842</t>
+          <t>2756</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11831</t>
+          <t>10865</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>20,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>10712</t>
+          <t>11893</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>12053</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>18805</t>
+          <t>18917</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>18148</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>12312</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>25225</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>33,79%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>22,92%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>46,96%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8982</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>4526</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>15216</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>16,89%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>28,61%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>18545</t>
+          <t>9840</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>25954</t>
+          <t>16524</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,48%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>27527</t>
+          <t>27988</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>19738</t>
+          <t>19866</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>36057</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>20,02%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>53715</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>53184</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>53184</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>53184</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>45510</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>45510</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>45510</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>58345</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>58345</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>58345</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>143</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>111529</t>
+          <t>99225</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111529</t>
+          <t>99225</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111529</t>
+          <t>99225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>43884</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>34122</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>56147</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>12,14%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>57540</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>44480</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>70550</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>12,81%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>9,9%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>15,7%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>49019</t>
+          <t>57485</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39331</t>
+          <t>46773</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>60507</t>
+          <t>71374</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>106559</t>
+          <t>101369</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>89835</t>
+          <t>86788</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>124884</t>
+          <t>119645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,53%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>90031</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>74478</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>108574</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>19,47%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>16,11%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>23,49%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>66164</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>51225</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>80844</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,73%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>11,4%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>17,99%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>97233</t>
+          <t>65023</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>79468</t>
+          <t>53697</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>115423</t>
+          <t>77292</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>12,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>18,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>163398</t>
+          <t>155054</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>139608</t>
+          <t>135821</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>189078</t>
+          <t>177999</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>17,19%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,89%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>103793</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>88264</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>119054</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>22,45%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>25,75%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>145</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>96938</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>76394</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>112981</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>21,58%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>17,0%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>25,15%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>113612</t>
+          <t>97949</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>95945</t>
+          <t>84088</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131848</t>
+          <t>113283</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>23,21%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>210550</t>
+          <t>201742</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>183415</t>
+          <t>180033</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>233983</t>
+          <t>224154</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>25,35%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>82598</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>65960</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>97871</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>17,87%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>14,27%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>21,17%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>121</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>84203</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>65759</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>99498</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>18,74%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14,64%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>22,14%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>86049</t>
+          <t>82674</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70072</t>
+          <t>70474</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102703</t>
+          <t>97551</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,98%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>170252</t>
+          <t>165272</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>148028</t>
+          <t>144304</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>193919</t>
+          <t>186099</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>69896</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>55760</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>88877</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>15,12%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>12,06%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>19,22%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>87474</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>61009</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>173694</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>19,47%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>38,66%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>74737</t>
+          <t>63749</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>58320</t>
+          <t>52677</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>93959</t>
+          <t>79286</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,1%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>162210</t>
+          <t>133645</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>130836</t>
+          <t>114480</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>242630</t>
+          <t>153454</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>72104</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>54734</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>100213</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>15,6%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11,84%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>21,68%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>82</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>56986</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>43575</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>72930</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>12,68%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>16,23%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>80620</t>
+          <t>55208</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>61724</t>
+          <t>44321</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>114374</t>
+          <t>67552</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,82%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>137605</t>
+          <t>127312</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>113578</t>
+          <t>107979</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>175854</t>
+          <t>159398</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,4%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>628</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>462306</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>462306</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>462306</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>623</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>449305</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>449305</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>449305</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>422088</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>422088</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>422088</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>501269</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>501269</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>501269</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1251</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>950574</t>
+          <t>884394</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>950574</t>
+          <t>884394</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>950574</t>
+          <t>884394</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>30731</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>22947</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>39707</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>18,44%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>13,77%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>23,82%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>33121</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>24565</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>42767</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>22,66%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>16,8%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>29,26%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>34139</t>
+          <t>33423</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>24590</t>
+          <t>24782</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45144</t>
+          <t>43302</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>67260</t>
+          <t>64154</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>54724</t>
+          <t>52310</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>82157</t>
+          <t>77359</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>51912</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>42600</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>63502</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>31,14%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>25,56%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>38,1%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>35826</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>28088</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>45259</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>24,51%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>19,21%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>30,96%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>57547</t>
+          <t>36274</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>47153</t>
+          <t>28417</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>71082</t>
+          <t>45049</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>30,62%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>93373</t>
+          <t>88186</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>80433</t>
+          <t>74443</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111565</t>
+          <t>101647</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>34,08%</t>
+          <t>32,39%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>37349</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>28960</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>48481</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>22,41%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>17,37%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>29,09%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>26312</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>18960</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>34231</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>18,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>12,97%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>23,42%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>39085</t>
+          <t>27144</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>29162</t>
+          <t>19637</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>49612</t>
+          <t>35724</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>65397</t>
+          <t>64493</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>52970</t>
+          <t>53218</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>78569</t>
+          <t>77171</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,59%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>28933</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>21224</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>38137</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>12,73%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>22,88%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>23173</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>16635</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>31513</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>15,85%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>11,38%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>21,56%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>22557</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>22492</t>
+          <t>15198</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41475</t>
+          <t>30626</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>54463</t>
+          <t>51490</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42773</t>
+          <t>40589</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>66652</t>
+          <t>63472</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,93%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,23%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>13020</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>7711</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>19838</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>7,81%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>4,63%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>11,9%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>15122</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>9906</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>22437</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6,78%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>15,35%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>13898</t>
+          <t>15400</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8965</t>
+          <t>9723</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21507</t>
+          <t>22577</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>29020</t>
+          <t>28420</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>20714</t>
+          <t>19992</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38391</t>
+          <t>36942</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,77%</t>
         </is>
       </c>
     </row>
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>4741</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2066</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9091</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2,84%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>5,45%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>12632</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>7586</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>19618</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>5,19%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>13,42%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>5179</t>
+          <t>12342</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>7179</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9940</t>
+          <t>19535</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>13,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,17 +2950,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>17811</t>
+          <t>17083</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11634</t>
+          <t>11917</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26298</t>
+          <t>25360</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>166686</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>222</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>146186</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>147140</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>147140</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>147140</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>181139</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>181139</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>181139</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>455</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>327324</t>
+          <t>313825</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>77418</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>64065</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>93351</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>11,34%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>13,67%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>92862</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>75935</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>110232</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>14,32%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>11,71%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>16,99%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>87059</t>
+          <t>92948</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>71916</t>
+          <t>79343</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>105058</t>
+          <t>109566</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>179921</t>
+          <t>170365</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>156934</t>
+          <t>151454</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>203571</t>
+          <t>192008</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,8%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>148281</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>128968</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>170691</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>21,72%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>18,89%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>25,0%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>165</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>109327</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>90011</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>129160</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>16,85%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>13,88%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>19,91%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>162173</t>
+          <t>107036</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>140045</t>
+          <t>92030</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>186041</t>
+          <t>124444</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>271500</t>
+          <t>255317</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>240054</t>
+          <t>229729</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>301333</t>
+          <t>280712</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>19,54%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>21,64%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>154617</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>135943</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>174878</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>22,65%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>19,91%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>25,62%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>139758</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>116548</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>162488</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>21,55%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>17,97%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>25,05%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>167350</t>
+          <t>137396</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>146559</t>
+          <t>119397</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>188540</t>
+          <t>156679</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,49%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>307108</t>
+          <t>292014</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>272159</t>
+          <t>265674</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>336429</t>
+          <t>319809</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,65%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>118808</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>101422</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>138677</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>17,4%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>14,86%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>20,31%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>119203</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>99901</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>140248</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>18,38%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>15,4%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>21,62%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>125468</t>
+          <t>114291</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>107541</t>
+          <t>98401</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>145141</t>
+          <t>130065</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>16,94%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>244671</t>
+          <t>233099</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>218191</t>
+          <t>208309</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>272756</t>
+          <t>259839</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,03%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>88589</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>71123</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>108099</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>12,98%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>15,83%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>108924</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>79571</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>193967</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>16,79%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>12,27%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>29,9%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>94359</t>
+          <t>85677</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>76601</t>
+          <t>71408</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>116508</t>
+          <t>102727</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,94%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>11,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>203283</t>
+          <t>174266</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>171357</t>
+          <t>152749</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>279004</t>
+          <t>196133</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>15,12%</t>
         </is>
       </c>
     </row>
@@ -3670,72 +3670,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>94993</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>76356</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>123374</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>13,91%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>11,18%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>18,07%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>112</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>78600</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>64263</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>96707</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>12,12%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>9,91%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>14,91%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>105</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>104343</t>
+          <t>77390</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>83954</t>
+          <t>62877</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>144583</t>
+          <t>91722</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>182943</t>
+          <t>172384</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>156323</t>
+          <t>149572</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>222235</t>
+          <t>202892</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,53%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -3783,74 +3783,74 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>682707</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>682707</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>682707</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>911</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>648675</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>648675</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>648675</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>614738</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>614738</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>614738</t>
+        </is>
+      </c>
+      <c r="N31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I31" s="2" t="inlineStr">
+      <c r="P31" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>938</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>740752</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
-        <is>
-          <t>740752</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr">
-        <is>
-          <t>740752</t>
-        </is>
-      </c>
-      <c r="N31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
           <t>1849</t>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1389427</t>
+          <t>1297444</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1389427</t>
+          <t>1297444</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1389427</t>
+          <t>1297444</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
